--- a/data/b2_bonsucesso/B2 Bonsucesso 12-2025.xlsx
+++ b/data/b2_bonsucesso/B2 Bonsucesso 12-2025.xlsx
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>64219.25</v>
+        <v>64187.63</v>
       </c>
     </row>
     <row r="3">
@@ -4828,25 +4828,25 @@
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>3807.12</v>
+        <v>4176.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>1256.35</v>
+        <v>2327.84</v>
       </c>
     </row>
     <row r="5">
@@ -4869,25 +4869,25 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>1355.68</v>
+        <v>1551.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46002</v>
+        <v>46004</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -4896,29 +4896,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>903.24</v>
+        <v>1541.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1423.56</v>
+        <v>1897.52</v>
       </c>
     </row>
     <row r="9">
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>4229.84</v>
+        <v>4038.26</v>
       </c>
     </row>
     <row r="10">
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>11212.81</v>
+        <v>11131.75</v>
       </c>
     </row>
     <row r="11">
@@ -4972,66 +4972,66 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1692.54</v>
+        <v>2408.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46009</v>
+        <v>46008</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Ampliação da pista de abastecimento</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>22000</v>
+        <v>1942.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46011</v>
+        <v>46009</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Ampliação da pista de abastecimento</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>22772.1</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46012</v>
+        <v>46011</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>4229.91</v>
+        <v>22940.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46013</v>
+        <v>46012</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -5040,29 +5040,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>2499.49</v>
+        <v>2686.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46015</v>
+        <v>46012</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>1038.57</v>
+        <v>4277.52</v>
       </c>
     </row>
     <row r="17">
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3998.9</v>
+        <v>3964.45</v>
       </c>
     </row>
     <row r="18">
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>1684.14</v>
+        <v>1629.76</v>
       </c>
     </row>
   </sheetData>
